--- a/hackground/public/assets/defaults/locality_excel_format/locality_excel_format.xlsx
+++ b/hackground/public/assets/defaults/locality_excel_format/locality_excel_format.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="46">
   <si>
     <t>latitude</t>
   </si>
@@ -37,7 +37,121 @@
     <t>city(city id)</t>
   </si>
   <si>
-    <t xml:space="preserve">[ ONE EXAMPLE PROVIDED ] </t>
+    <t>type</t>
+  </si>
+  <si>
+    <t>distance</t>
+  </si>
+  <si>
+    <t>metro_or_rail</t>
+  </si>
+  <si>
+    <t>Bullyguange</t>
+  </si>
+  <si>
+    <t>market</t>
+  </si>
+  <si>
+    <t>kasba Market</t>
+  </si>
+  <si>
+    <t>school</t>
+  </si>
+  <si>
+    <t>Ruby Park</t>
+  </si>
+  <si>
+    <t>hospital</t>
+  </si>
+  <si>
+    <t>Ruby General Hospital</t>
+  </si>
+  <si>
+    <t>روبي بارك</t>
+  </si>
+  <si>
+    <t>مستشفى روبي</t>
+  </si>
+  <si>
+    <t>govt_entities</t>
+  </si>
+  <si>
+    <t>GST Bhawan</t>
+  </si>
+  <si>
+    <t>مبنى الضرائب</t>
+  </si>
+  <si>
+    <t>Esplanade</t>
+  </si>
+  <si>
+    <t>إيسبلانيد</t>
+  </si>
+  <si>
+    <t>Esplanade Metro</t>
+  </si>
+  <si>
+    <t>مترو إيسبلانيد</t>
+  </si>
+  <si>
+    <t>New Market</t>
+  </si>
+  <si>
+    <t>السوق الجديد</t>
+  </si>
+  <si>
+    <t>St. Xavier's</t>
+  </si>
+  <si>
+    <t>سانت كزافييه</t>
+  </si>
+  <si>
+    <t>Calcutta Medical College</t>
+  </si>
+  <si>
+    <t>كلية الطب</t>
+  </si>
+  <si>
+    <t>Writer's Building</t>
+  </si>
+  <si>
+    <t>مبنى الكُتّاب</t>
+  </si>
+  <si>
+    <t>Tollygunge</t>
+  </si>
+  <si>
+    <t>توليغونج</t>
+  </si>
+  <si>
+    <t>Tollygunge Metro</t>
+  </si>
+  <si>
+    <t>مترو توليغونج</t>
+  </si>
+  <si>
+    <t>Lake Market</t>
+  </si>
+  <si>
+    <t>سوق لايك</t>
+  </si>
+  <si>
+    <t>South Point</t>
+  </si>
+  <si>
+    <t>ساوث بوينت</t>
+  </si>
+  <si>
+    <t>RSV Hospital</t>
+  </si>
+  <si>
+    <t>مستشفى RSV</t>
+  </si>
+  <si>
+    <t>Tollygunge Police Station</t>
+  </si>
+  <si>
+    <t>مركز شرطة توليغونج</t>
   </si>
 </sst>
 </file>
@@ -398,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -407,9 +521,11 @@
     <col min="4" max="4" width="13.33203125" customWidth="1"/>
     <col min="5" max="5" width="20.21875" customWidth="1"/>
     <col min="6" max="6" width="25.33203125" customWidth="1"/>
+    <col min="7" max="7" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -425,125 +541,453 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>22.5867</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>88.417299999999997</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>22.5867</v>
+      </c>
+      <c r="C3">
+        <v>88.417299999999997</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>22.5867</v>
+      </c>
+      <c r="C4">
+        <v>88.417299999999997</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>22.5867</v>
+      </c>
+      <c r="C5">
+        <v>88.417299999999997</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>22.5867</v>
+      </c>
+      <c r="C6">
+        <v>88.417299999999997</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>22.572600000000001</v>
+      </c>
+      <c r="C7">
+        <v>88.363900000000001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>22.572600000000001</v>
+      </c>
+      <c r="C8">
+        <v>88.363900000000001</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>22.572600000000001</v>
+      </c>
+      <c r="C9">
+        <v>88.363900000000001</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>22.572600000000001</v>
+      </c>
+      <c r="C10">
+        <v>88.363900000000001</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>22.572600000000001</v>
+      </c>
+      <c r="C11">
+        <v>88.363900000000001</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>22.499199999999998</v>
+      </c>
+      <c r="C12">
+        <v>88.320099999999996</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>22.499199999999998</v>
+      </c>
+      <c r="C13">
+        <v>88.320099999999996</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>22.499199999999998</v>
+      </c>
+      <c r="C14">
+        <v>88.320099999999996</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>22.499199999999998</v>
+      </c>
+      <c r="C15">
+        <v>88.320099999999996</v>
+      </c>
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>22.499199999999998</v>
+      </c>
+      <c r="C16">
+        <v>88.320099999999996</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2"/>
